--- a/Data/Commodore-Repair-Toolbox.xlsx
+++ b/Data/Commodore-Repair-Toolbox.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data\Development\Visual Studio\Commodore-Repair-Toolbox\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F671B3DE-DD10-46AF-B644-CE9CCB6E0A86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687CCEA7-F368-4A68-A5E1-ACE497E402C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="22932" yWindow="-108" windowWidth="23256" windowHeight="14016" xr2:uid="{EBC5E150-CC27-441B-9E4F-9F7CF77570D6}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="38">
   <si>
     <t>Hardware name in drop-down</t>
   </si>
@@ -171,8 +171,11 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>2026-March-2</t>
+      <t>2026-March-7</t>
     </r>
+  </si>
+  <si>
+    <t>2026-March-7</t>
   </si>
 </sst>
 </file>
@@ -913,7 +916,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56206CAE-0631-4609-AB22-50D6669B86E2}">
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="85.5546875" customWidth="1"/>
@@ -970,6 +973,11 @@
         <v>35</v>
       </c>
     </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" location="main-excel-data-file-format" xr:uid="{9927CEA5-CE63-49AA-96B9-BF7942EAA073}"/>
